--- a/event_registration_forms/014_data_visualization_training_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/014_data_visualization_training_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'data_scientist',_'label':_'data_scientist'}</t>
+          <t>data_scientist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Data Scientist', 'label': 'Data Scientist'}</t>
+          <t>Data Scientist</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'data_analyst',_'label':_'data_analyst'}</t>
+          <t>data_analyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Data Analyst', 'label': 'Data Analyst'}</t>
+          <t>Data Analyst</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'on-site',_'label':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'On-site', 'label': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'half-day',_'label':_'half-day'}</t>
+          <t>half-day</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Half-day', 'label': 'Half-day'}</t>
+          <t>Half-day</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'full-day',_'label':_'full-day'}</t>
+          <t>full-day</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Full-day', 'label': 'Full-day'}</t>
+          <t>Full-day</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'multi-day',_'label':_'multi-day'}</t>
+          <t>multi-day</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Multi-day', 'label': 'Multi-day'}</t>
+          <t>Multi-day</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'in-person',_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'In-person', 'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'mandarin',_'label':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Mandarin', 'label': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'instructor_1',_'label':_'instructor_1'}</t>
+          <t>instructor_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Instructor 1', 'label': 'Instructor 1'}</t>
+          <t>Instructor 1</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'instructor_2',_'label':_'instructor_2'}</t>
+          <t>instructor_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Instructor 2', 'label': 'Instructor 2'}</t>
+          <t>Instructor 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'instructor_3',_'label':_'instructor_3'}</t>
+          <t>instructor_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Instructor 3', 'label': 'Instructor 3'}</t>
+          <t>Instructor 3</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'course_1',_'label':_'course_1'}</t>
+          <t>course_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Course 1', 'label': 'Course 1'}</t>
+          <t>Course 1</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'course_2',_'label':_'course_2'}</t>
+          <t>course_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Course 2', 'label': 'Course 2'}</t>
+          <t>Course 2</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'course_3',_'label':_'course_3'}</t>
+          <t>course_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Course 3', 'label': 'Course 3'}</t>
+          <t>Course 3</t>
         </is>
       </c>
     </row>
